--- a/assets/constructions/examples/ctd_tavs_head.xlsx
+++ b/assets/constructions/examples/ctd_tavs_head.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,11 +539,31 @@
           <t>cict</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VAS32-IR3222-3</t>
+          <t>VAS32-IR3222-4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -563,7 +583,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>VARGUS_3/8IR</t>
+          <t>VARGUS_1/2IR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -575,7 +595,7 @@
         <v>32.3</v>
       </c>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>22.7</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -615,11 +635,25 @@
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>326.32</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>28677.85</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VAS32-IR3222-4</t>
+          <t>VAS40-IR3627-5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -629,29 +663,29 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VARGUS_5/8IR</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>VARGUS_VAS:40</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>40</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>VARGUS_1/2IR</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>VARGUS_VAS:32</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>32.3</v>
-      </c>
       <c r="J3" t="n">
-        <v>22.7</v>
+        <v>27.3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -691,11 +725,25 @@
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>407.14</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>35780.52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VAS40-IR3227-4</t>
+          <t>VAS25-IR2517-3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -705,29 +753,29 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F4" t="n">
         <v>32</v>
       </c>
-      <c r="E4" t="n">
-        <v>40</v>
-      </c>
-      <c r="F4" t="n">
-        <v>50</v>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>VARGUS_1/2IR</t>
+          <t>VARGUS_3/8IR</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>VARGUS_VAS:40</t>
+          <t>VARGUS_VAS:25</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>40</v>
+        <v>25.3</v>
       </c>
       <c r="J4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -767,11 +815,25 @@
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>283.32</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>24898.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VAS40-IR3627-5</t>
+          <t>VAS40-IR3227-4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -781,7 +843,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
         <v>40</v>
@@ -791,7 +853,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>VARGUS_5/8IR</t>
+          <t>VARGUS_1/2IR</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -803,7 +865,7 @@
         <v>40</v>
       </c>
       <c r="J5" t="n">
-        <v>27.3</v>
+        <v>27</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -843,11 +905,25 @@
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>383.94</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>33741.65</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAS25-IR2517-3</t>
+          <t>VAS40-IR3227-3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -857,13 +933,13 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -872,14 +948,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>VARGUS_VAS:25</t>
+          <t>VARGUS_VAS:40</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>25.3</v>
+        <v>40</v>
       </c>
       <c r="J6" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -919,6 +995,20 @@
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>375</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>32955.98</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
